--- a/data/wfa_stock_results_2024-10-21_2026-04-20.xlsx
+++ b/data/wfa_stock_results_2024-10-21_2026-04-20.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="36357480-b1ef-48bc-8283-74e064d" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="657882e3-93e7-4831-b426-d31623c" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="98">
   <si>
     <t xml:space="preserve">sektor</t>
   </si>
@@ -67,6 +67,12 @@
     <t xml:space="preserve">MA_Crossover_Signal</t>
   </si>
   <si>
+    <t xml:space="preserve">RSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSI_Signal</t>
+  </si>
+  <si>
     <t xml:space="preserve">ADRO</t>
   </si>
   <si>
@@ -128,12 +134,6 @@
   </si>
   <si>
     <t xml:space="preserve">BBCA.JK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSI_Signal</t>
   </si>
   <si>
     <t xml:space="preserve">BBNI</t>
@@ -515,7 +515,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.8"/>
@@ -579,19 +579,19 @@
         <v>14</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>85.7142857142857</v>
+        <v>100</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -599,31 +599,31 @@
         <v>10</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>58.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -643,13 +643,13 @@
         <v>14</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="0" t="n">
         <v>50</v>
@@ -663,31 +663,31 @@
         <v>10</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -695,10 +695,10 @@
         <v>10</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>13</v>
@@ -707,19 +707,19 @@
         <v>14</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>75</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -727,31 +727,31 @@
         <v>10</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <v>3</v>
-      </c>
       <c r="H7" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>25</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -759,10 +759,10 @@
         <v>10</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>13</v>
@@ -771,19 +771,19 @@
         <v>14</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -791,31 +791,31 @@
         <v>10</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="0" t="n">
         <v>5</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>50</v>
+        <v>58.3333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -823,10 +823,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>13</v>
@@ -835,19 +835,19 @@
         <v>14</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -855,25 +855,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I11" s="0" t="n">
         <v>100</v>
@@ -884,13 +884,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>13</v>
@@ -899,62 +899,62 @@
         <v>14</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>13</v>
@@ -963,62 +963,62 @@
         <v>14</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" s="0" t="n">
         <v>66.6666666666667</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>13</v>
@@ -1027,42 +1027,42 @@
         <v>14</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="0" t="n">
         <v>0</v>
@@ -1076,13 +1076,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>13</v>
@@ -1091,62 +1091,62 @@
         <v>14</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>80</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>40</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>44</v>
-      </c>
       <c r="C20" s="0" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>13</v>
@@ -1155,62 +1155,62 @@
         <v>14</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>44</v>
-      </c>
       <c r="C21" s="0" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="0" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>13</v>
@@ -1219,62 +1219,62 @@
         <v>14</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>13</v>
@@ -1283,126 +1283,126 @@
         <v>14</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H25" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="0" t="n">
-        <v>40</v>
-      </c>
       <c r="J26" s="0" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F27" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I27" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>13</v>
@@ -1411,62 +1411,62 @@
         <v>14</v>
       </c>
       <c r="F28" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="0" t="n">
-        <v>22.2222222222222</v>
+        <v>25</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>27.7777777777778</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F29" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>13</v>
@@ -1475,62 +1475,62 @@
         <v>14</v>
       </c>
       <c r="F30" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>100</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F31" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>13</v>
@@ -1539,62 +1539,62 @@
         <v>14</v>
       </c>
       <c r="F32" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F33" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" s="0" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>13</v>
@@ -1603,62 +1603,62 @@
         <v>14</v>
       </c>
       <c r="F34" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G34" s="0" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I34" s="0" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>70.8333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F35" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" s="0" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35" s="0" t="n">
-        <v>75</v>
+        <v>12.5</v>
       </c>
       <c r="J35" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>13</v>
@@ -1667,39 +1667,39 @@
         <v>14</v>
       </c>
       <c r="F36" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G36" s="0" t="n">
         <v>4</v>
       </c>
       <c r="H36" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36" s="0" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F37" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" s="0" t="n">
         <v>2</v>
@@ -1716,13 +1716,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>13</v>
@@ -1731,62 +1731,62 @@
         <v>14</v>
       </c>
       <c r="F38" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J38" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F39" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H39" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I39" s="0" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J39" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>13</v>
@@ -1795,62 +1795,62 @@
         <v>14</v>
       </c>
       <c r="F40" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H40" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J40" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F41" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G41" s="0" t="n">
         <v>6</v>
       </c>
       <c r="H41" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="0" t="n">
-        <v>50</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="J41" s="0" t="n">
-        <v>41.6666666666667</v>
+        <v>72.2222222222222</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>13</v>
@@ -1862,59 +1862,59 @@
         <v>3</v>
       </c>
       <c r="G42" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H42" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F43" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>13</v>
@@ -1926,59 +1926,59 @@
         <v>3</v>
       </c>
       <c r="G44" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="0" t="n">
-        <v>100</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>100</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F45" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H45" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I45" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>13</v>
@@ -1990,59 +1990,59 @@
         <v>3</v>
       </c>
       <c r="G46" s="0" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H46" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" s="0" t="n">
-        <v>50</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="J46" s="0" t="n">
-        <v>50</v>
+        <v>77.7777777777778</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F47" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>13</v>
@@ -2054,59 +2054,59 @@
         <v>3</v>
       </c>
       <c r="G48" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="0" t="n">
-        <v>100</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="J48" s="0" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F49" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H49" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>13</v>
@@ -2118,59 +2118,59 @@
         <v>3</v>
       </c>
       <c r="G50" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I50" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F51" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I51" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D52" s="0" t="s">
         <v>13</v>
@@ -2182,59 +2182,59 @@
         <v>3</v>
       </c>
       <c r="G52" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H52" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F53" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I53" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>13</v>
@@ -2246,33 +2246,33 @@
         <v>3</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F55" s="0" t="n">
         <v>1</v>
@@ -2281,24 +2281,24 @@
         <v>2</v>
       </c>
       <c r="H55" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J55" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>13</v>
@@ -2310,59 +2310,59 @@
         <v>3</v>
       </c>
       <c r="G56" s="0" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H56" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" s="0" t="n">
-        <v>40</v>
+        <v>57.1428571428571</v>
       </c>
       <c r="J56" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>55.5555555555556</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F57" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I57" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>13</v>
@@ -2377,56 +2377,56 @@
         <v>2</v>
       </c>
       <c r="H58" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F59" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>13</v>
@@ -2438,48 +2438,688 @@
         <v>3</v>
       </c>
       <c r="G60" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>40</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>25</v>
+        <v>22.2222222222222</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B62" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="J62" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="J66" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="0" t="n">
+        <v>66.6666666666667</v>
+      </c>
+      <c r="J67" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="J69" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="0" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="J70" s="0" t="n">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F71" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H71" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" s="0" t="n">
+        <v>28.5714285714286</v>
+      </c>
+      <c r="J71" s="0" t="n">
+        <v>16.6666666666667</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="J72" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="J75" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="J76" s="0" t="n">
+        <v>66.6666666666667</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H77" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="0" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="J77" s="0" t="n">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="J78" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C61" s="0" t="s">
+      <c r="C80" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="E61" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="F61" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="I61" s="0" t="n">
-        <v>66.6666666666667</v>
-      </c>
-      <c r="J61" s="0" t="n">
-        <v>66.6666666666667</v>
+      <c r="D80" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
